--- a/Speciallægeloft/speciallægeloft_data/Nykøbing_F.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Nykøbing_F.xlsx
@@ -70,7 +70,7 @@
     <t>Datasæt 12 2024</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 13.04.59</t>
+    <t>Kørsel 15.4.2026 14.35.11</t>
   </si>
   <si>
     <t/>
